--- a/frontend/public/weekly_contest_3_leaderboard.xlsx
+++ b/frontend/public/weekly_contest_3_leaderboard.xlsx
@@ -142,7 +142,7 @@
     <t xml:space="preserve">B. Shreya Kamath</t>
   </si>
   <si>
-    <t xml:space="preserve">bshreyakamath@gmail.com</t>
+    <t xml:space="preserve">nnm24am015@nmamit.in</t>
   </si>
   <si>
     <t xml:space="preserve">Anvith C Bhagavath</t>
@@ -396,28 +396,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -613,31 +617,31 @@
   <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="17.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -654,10 +658,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="4" t="n">
@@ -671,10 +675,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
@@ -688,10 +692,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="n">
@@ -705,10 +709,10 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
@@ -722,10 +726,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
@@ -739,10 +743,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
@@ -756,10 +760,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4" t="n">
@@ -773,10 +777,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="4" t="n">
@@ -790,10 +794,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="4" t="n">
@@ -807,10 +811,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="4" t="n">
@@ -824,10 +828,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="4" t="n">
@@ -841,10 +845,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="4" t="n">
@@ -858,10 +862,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="4" t="n">
@@ -875,10 +879,10 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="4" t="n">
@@ -892,10 +896,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C17" s="4" t="n">
@@ -909,10 +913,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="4" t="n">
@@ -926,10 +930,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="4" t="n">
@@ -943,10 +947,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="4" t="n">
@@ -960,10 +964,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="4" t="n">
@@ -977,10 +981,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="4" t="n">
@@ -994,10 +998,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="4" t="n">
@@ -1011,10 +1015,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="4" t="n">
@@ -1028,10 +1032,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C25" s="4" t="n">
@@ -1045,10 +1049,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="4" t="n">
@@ -1062,10 +1066,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C27" s="4" t="n">
@@ -1079,10 +1083,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="4" t="n">
@@ -1096,10 +1100,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="4" t="n">
@@ -1113,10 +1117,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="4" t="n">
@@ -1130,10 +1134,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="4" t="n">
@@ -1147,10 +1151,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="4" t="n">
@@ -1164,10 +1168,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="4" t="n">
@@ -1181,10 +1185,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="4" t="n">
@@ -1198,10 +1202,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C35" s="4" t="n">
@@ -1215,10 +1219,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="4" t="n">
@@ -1232,10 +1236,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="4" t="n">
@@ -1249,10 +1253,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="4" t="n">
@@ -1266,10 +1270,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C39" s="4" t="n">
@@ -1283,10 +1287,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C40" s="4" t="n">
@@ -1300,10 +1304,10 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="4" t="n">
@@ -1317,10 +1321,10 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C42" s="4" t="n">
@@ -1334,10 +1338,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C43" s="4" t="n">
@@ -1351,10 +1355,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C44" s="4" t="n">
@@ -1368,10 +1372,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="4" t="n">
@@ -1387,6 +1391,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="sandeeppaikulyadi05@gmail.com"/>
+    <hyperlink ref="B19" r:id="rId2" display="nnm24am015@nmamit.in"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
